--- a/ig/DM-AVRIL-2026/ValueSet-JDV-J281-StatutsRessourcesMS.xlsx
+++ b/ig/DM-AVRIL-2026/ValueSet-JDV-J281-StatutsRessourcesMS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-05-05T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -151,6 +151,12 @@
   </si>
   <si>
     <t>En pause</t>
+  </si>
+  <si>
+    <t>FACTURE</t>
+  </si>
+  <si>
+    <t>Facturé</t>
   </si>
   <si>
     <t/>
@@ -421,7 +427,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -513,15 +519,23 @@
         <v>46</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>48</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
